--- a/EPIC_0007_Wallets_Payments.xlsx
+++ b/EPIC_0007_Wallets_Payments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1B1FD9-C890-4692-A542-B599BF35DEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA88A24-020A-491D-B279-CC674E5E755E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -312,9 +312,6 @@
   </si>
   <si>
     <t>Driver App Wallet Verification</t>
-  </si>
-  <si>
-    <t>TC_RG_01_Driver_App_Wallet_Verification</t>
   </si>
   <si>
     <t>This end-to-end hybrid regression test verifies the runtime visibility and functionality of the mobile Driver Wallet module based on configurations managed within the Super Admin Web Portal. The execution workflow first activates the wallet feature via the admin portal's site settings, logs into the driver application, and executes a full simulated wallet top-up transaction using Net Banking to confirm operational stability. It then reverts to the web panel to toggle the wallet status to "OFF," restarts the mobile application context to clear active sessions, re-authenticates the driver, and explicitly asserts that the Wallet option is completely absent from the side menu hierarchy.</t>
@@ -411,9 +408,6 @@
   </si>
   <si>
     <t>Customer App Wallet Verification</t>
-  </si>
-  <si>
-    <t>TC_RG_02_Customer_App_Wallet_Verification</t>
   </si>
   <si>
     <t>This end-to-end hybrid regression test verifies the runtime visibility and functionality of the mobile Customer Wallet module based on configurations managed within the Super Admin Web Portal. The execution workflow first activates the wallet feature via the admin portal's site settings, logs into the customer application, and executes a full simulated wallet top-up transaction using Net Banking to confirm operational stability. It then reverts to the web panel to toggle the wallet status to "OFF," restarts the mobile application context to clear active sessions, re-authenticates the customer, and explicitly asserts that the Wallet option is completely absent from the side menu hierarchy.</t>
@@ -665,6 +659,12 @@
 70.Click Submit Button,click,,"web.global.action.submit"
 71.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
 72.Wait For Toast To Hide,wait,3000,</t>
+  </si>
+  <si>
+    <t>TC_RG_02_Driver_App_Wallet_Verification</t>
+  </si>
+  <si>
+    <t>TC_RG_03_Customer_App_Wallet_Verification</t>
   </si>
 </sst>
 </file>
@@ -1166,22 +1166,22 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J2" s="2"/>
     </row>
@@ -1258,31 +1258,31 @@
         <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">

--- a/EPIC_0007_Wallets_Payments.xlsx
+++ b/EPIC_0007_Wallets_Payments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA88A24-020A-491D-B279-CC674E5E755E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80908BEB-778A-4735-88BB-C6FC7998ED2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserDriverWebIntialilzer" sheetId="43" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>Requirement Title</t>
   </si>
@@ -488,6 +488,18 @@
 70. Wait 3 seconds for the toast notification to hide.</t>
   </si>
   <si>
+    <t>34.Click Wallet,tap,,"mobile.customer.wallet.btn"
+35.Wait For Topup,wait_until_visible,,"mobile.customer.top_up.btn"
+36.Check Current Balance Displayed,element_present,,"mobile.customer.wallet.current_balance"
+37.Check Transaction History Displaye,element_present,,"mobile.customer.wallet.transaction_history"</t>
+  </si>
+  <si>
+    <t>TC_RG_02_Driver_App_Wallet_Verification</t>
+  </si>
+  <si>
+    <t>TC_RG_03_Customer_App_Wallet_Verification</t>
+  </si>
+  <si>
     <t>1. Load Driver App,switch_to,driver,
 2.Reload Driver App Completely,reload_app,driver,
 3. Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
@@ -539,52 +551,224 @@
 49.Wait For Success,wait_until_visible,,"mobile.driver.top_up.succes_popup"
 50.Click Success,tap,,"mobile.driver.top_up.succes_popup"
 51.Wait For Wallet  Back,wait_until_visible,,"mobile.driver.wallet.btn"
-52.Click Back,tap,,"mobile.driver.back.btn"
-53.Drag Page Layout Upward,swipe,up,
-54.Click Back,tap,,"mobile.driver.back.btn"
-55.Reload Driver App Completely,reload_app,driver,
-56. Switch To Web Session,switch_to,web,
-57.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-58. Click Settings Menu,click,,"admin.setting.sidebar.menu"
-59. Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
-60. Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
-61.Wait For off,wait,2000,
-62. Select Wallet OFF Option,click,,"admin.setting.site_setting.walletdropdown_option_off"
-63. Click Submit Button,click,,"web.global.action.submit"
-64. Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
-65. Switch To Driver Session,switch_to,driver,
-66. Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
-67. Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
-68. Click Agree,tap,,"mobile.driver.agree.btn"
-68. Click Get Started,tap,,"mobile.driver.get_started.btn"
-70. Click Next,tap,,"mobile.driver.next.btn"
-71. Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
-72. Click Close,tap,,"mobile.driver.cancel.btn"
-73. Enter Mobile Number,type,regression.approved_driver.phone ,"mobile.driver.edit_text.input"
-74. Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
-75. Click Continue,tap,,"mobile.driver.continue.btn"
-76. Enter OTP,type,123456,"mobile.driver.edit_text.input"
-77. Click Allow Location,tap,,"mobile.driver.location_allow.btn"
-78. Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
-79.Click Hamburger,tap_coordinate,75:209,COORDINATE_MODE
-80.Wait For Account,wait_until_visible,,"mobile.driver.account.heading"
-81.Check Wallet absent,element_absent,,"mobile.driver.wallet.btn"
-82.Load Super Admin,switch_to,web,
-83.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-84.Click Settings Menu,click,,"web.global.menu.settings"
-85.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
-86.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
-87.Wait For On,wait,2000,
-88.Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
-89.Click Submit Button,click,,"web.global.action.submit"
-90.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
-91.Wait For Toast To Hide,wait,3000,</t>
-  </si>
-  <si>
-    <t>34.Click Wallet,tap,,"mobile.customer.wallet.btn"
-35.Wait For Topup,wait_until_visible,,"mobile.customer.top_up.btn"
-36.Check Current Balance Displayed,element_present,,"mobile.customer.wallet.current_balance"
-37.Check Transaction History Displaye,element_present,,"mobile.customer.wallet.transaction_history"</t>
+52.Click Pay button,tap,,"mobile.driver.wallet_pay.btn"
+53.Click Benefical Search,tap,,"mobile.driver.wallet_pay.beneficial_search"
+54.Search Benfical Name,type,regression,"mobile.driver.wallet_pay.beneficial_search_Field"
+55.Enter Benfical Name,press_enter,,"mobile.driver.wallet_pay.beneficial_search_Field"
+56.Wait To Load,wait,3000
+57.Select Benefical,tap,,"mobile.driver.wallet_pay.beneficial_select"
+58.Enter Transfer Amout,type,100,"mobile.driver.wallet_pay.amount_field"
+59.Click Transfer Button,tap,,"mobile.driver.wallet_pay.transfer_btn"
+60.Wait For Transfer,wait,2000,
+61.Click Transfer Ok,tap,,"mobile.driver.wallet_pay.transfer_ok_btn"
+62.Wait For Wallet  Back,wait_until_visible,,"mobile.driver.wallet.btn"
+63.Click Back,tap,,"mobile.driver.back.btn"
+64.Drag Page Layout Upward,swipe,up,
+65.Click Back,tap,,"mobile.driver.back.btn"
+66.Reload Driver App Completely,reload_app,driver,
+67. Switch To Web Session,switch_to,web,
+68.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+69. Click Settings Menu,click,,"admin.setting.sidebar.menu"
+70. Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+71. Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+72.Wait For off,wait,2000,
+73. Select Wallet OFF Option,click,,"admin.setting.site_setting.walletdropdown_option_off"
+74. Click Submit Button,click,,"web.global.action.submit"
+75. Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+76. Switch To Driver Session,switch_to,driver,
+77. Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+78. Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+79. Click Agree,tap,,"mobile.driver.agree.btn"
+80. Click Get Started,tap,,"mobile.driver.get_started.btn"
+81. Click Next,tap,,"mobile.driver.next.btn"
+82. Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+83. Click Close,tap,,"mobile.driver.cancel.btn"
+84. Enter Mobile Number,type,regression.approved_driver.phone ,"mobile.driver.edit_text.input"
+85. Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+86. Click Continue,tap,,"mobile.driver.continue.btn"
+87. Enter OTP,type,123456,"mobile.driver.edit_text.input"
+88. Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+89. Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+90.Click Hamburger,tap_coordinate,75:209,COORDINATE_MODE
+91.Wait For Account,wait_until_visible,,"mobile.driver.account.heading"
+92.Check Wallet absent,element_absent,,"mobile.driver.wallet.btn"
+93.Load Super Admin,switch_to,web,
+94.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+95.Click Settings Menu,click,,"web.global.menu.settings"
+96.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+97.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+98.Wait For On,wait,2000,
+99.Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
+100.Click Submit Button,click,,"web.global.action.submit"
+101.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+102.Wait For Toast To Hide,wait,3000,</t>
+  </si>
+  <si>
+    <t>1.Reload Driver App Completely,reload_app,driver,
+2.Load Super Admin,switch_to,web,
+3.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+4.Click Settings Menu,click,,"web.global.menu.settings"
+5.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+6.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+7.Wait For On,wait,2000,
+8.Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
+9.Click Submit Button,click,,"web.global.action.submit"
+10.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+11.Wait For Toast To Hide,wait,3000,
+12.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+13.Click drivers menu,click,,"admin.drivers.menu.icon"
+14.Click Add Driver menu,click,,"admin.drivers.add_menu.link"
+15.Verify Add Driver,verify,,"admin.drivers.add_page.header"
+16.Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
+17.Select Auto Ride Option,click,,"admin.drivers.service_dropdown.auto_ride"
+18.Click Driver Type Dropdown,click,,"admin.drivers.driver_type.dropdown"
+19.Select pilot Option,click,,"admin.drivers.driver_type.dropdown_pilot"
+20.Enter Driver Name, type, autodriver{randomAlpha} &gt;&gt; autoName, "admin.drivers.fullname.input"
+21.Enter Email, type, autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail, "admin.drivers.email.input"
+22.Enter Contact Number, type, {randomPhone}&gt;&gt;autoPhone, "admin.drivers.phone.input"
+23.Click Whatspp, click, , "admin.drivers.whatsapp.checkbox"
+24.Enter Whatspp Number, type, {autoPhone}, "admin.drivers.whatsapp_phone.input"
+25.Upload Profile Image, uploadfile, "src/main/resources/test-data/autodriver.jpg", "admin.drivers.profile_image.file"
+26.Select Source,click,,"admin.drivers.source_dropdown.select"
+27.Select Instagram,click,,"admin.drivers.instagram_option.span"
+28.Select Male Gender, click, , "admin.drivers.male_gender.div"
+29.Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+30. Select  Auto Option,click,,"admin.drivers.vehicle_option.pinkauto"
+31. Enter Model Year, type, 2013, "admin.drivers.modelyear.input"
+32. Enter Plate No, type, KL-01-AB-1234, "admin.drivers.plateno.input"
+33. Enter Model Name, type, petrol, "admin.drivers.modelname.input"
+34. Upload Vehicle Image, uploadfile, "src/main/resources/test-data/vehicle.jpg", "admin.drivers.vehicle_image.file"
+35. Enter Bank Name, type, HDFC Bank, "admin.drivers.bankname.input"
+36. Enter Bank Location, type, PARK STREET, "admin.drivers.banklocation.input"
+37. Enter Account Number, type, 50100123456789, "admin.drivers.accountno.input"
+38. Enter Account Holder Name, type,{autoName}, "admin.drivers.accountholder.input"
+39. Enter Payment Email Address, type, {autoEmail}, "admin.drivers.paymentemail.input"
+40. Enter IFSC Code, type, HDFC0001234, "admin.drivers.ifsc.input"
+41. Click Submit, click, , "web.global.action.submit"
+42. Verify Driver Added, verify,, "web.global.toast.success"
+43. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+44. Click drivers menu,click,,"admin.drivers.menu.icon"
+45. Click Pending Documents,click,,"admin.drivers.pending_docs.link"
+46. Filter by Name,type,{autoName},"admin.drivers.name_filter.input"
+47. Scroll Grid, tab, 7, "admin.drivers.name_filter.input"
+48. Click Doc Icon,click,,"admin.drivers.docs.icon"
+49. Driver Required Documents,verify,,"admin.drivers.required_docs.header"
+50. FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
+51. Add Driving License,click,,"admin.drivers.docs.edit_icon"
+52. Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+53. Enter Expiry Date,set_date,2026-12-12,"admin.drivers.doc_expiry.input"
+54. Click Submit, click, , "web.global.action.submit"
+55. Verify Updated Succesfully, verify, , "web.global.toast.updated"
+56. Click Approve Driver,click,,"admin.drivers.docs.approval"
+57. Verify Updated Succesfully, verify, , "web.global.toast.updated"
+58. Click Dashboard,click,,"web.global.menu.dashboard"
+59. Click drivers menu,click,,"admin.drivers.menu.icon"
+60. Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
+61. Approved Drivers List,verify,,"admin.drivers.approved_page.header"
+62. Filter Approved Driver,type,{autoName},"admin.drivers.name_filter.input"
+63.Wait For Load,wait,2000,
+64.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
+65.Click Wallet,click,,"admin.drivers.wallet.btn"
+66.Click Manage Transaction,click,,"admin.drivers.wallet.manage_transaction.btn"
+67.Enter Wallet Amout,type,500,"admin.drivers.wallet.wallet_amount_input"
+68.Click Dropdown,click,,"admin.drivers.wallet.option_dropdown"
+69.Select Add Money Optin,click,,"admin.drivers.wallet.option_add_money"
+70.Click Submit Button,click,,"admin.drivers.wallet.submit.btn"
+71.Wait For Recharge,wait,2000,
+72.Load Driver App,switch_to,driver,
+73.Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+74.Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+75.Click Agree,tap,,"mobile.driver.agree.btn"
+76. Click Get Started,tap,,"mobile.driver.get_started.btn"
+77.Click Next,tap,,"mobile.driver.next.btn"
+78.Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+79.Click Close,tap,,"mobile.driver.cancel.btn"
+80. Enter Mobile Number,type,{autoPhone},"mobile.driver.edit_text.input"
+81.Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+82.Click Continue,tap,,"mobile.driver.continue.btn"
+83.Enter OTP,type,123456,"mobile.driver.edit_text.input"
+84.Enter Account Holder,type,{autoName},"mobile.driver.bank_details.account_holder_name"
+85.Enter Account Number,type,50100123456789,"mobile.driver.bank_details.account_number"
+86.Enter Confirm Account Number,type,50100123456789,"mobile.driver.bank_details.confirm_account_number"
+87.Enter IFSC Code,type,HDFC0001234,"mobile.driver.bank_details.confirm_ifsc_code"
+88.Wait For Keyboard Minimises,hide_keyboard,,
+89.Enter Upi Id,type,sujanpariyar07@fam,"mobile.driver.bank_details.upi_id"
+90.Wait For Keyboard Minimises,hide_keyboard,,
+91.Click Submit,click,,"mobile.driver.bank_details.submit_btn"
+92.Force Driver Location To Perambur,set_location,13.121030;80.232578,
+93.Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+94.Wait for Toast to Hide,wait,3000,,
+95.Click Select All Agree,tap,,"mobile.driver.independent_contractor.checkbox_Select_All"
+96.Wait for Agree,wait_until_visible,,"mobile.driver.agree_continue.btn"
+97.Click Agree,tap,,"mobile.driver.agree_continue.btn"
+98.Wait For OTP,wait_until_visible,,"mobile.driver.edit_text.input"
+99. Enter OTP,type,123456,"mobile.driver.edit_text.input"
+100. Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+101.Wait For Hamburger Menu,wait,3000
+102.Click Hamburger,tap_coordinate,75:209,COORDINATE_MODE
+103.wait for Bank Details,wait_until_visible,"mobile.driver.bank_details.btn"
+104.Click Bank Details,tap,,"mobile.driver.bank_details.btn"
+105.Wait For Back,wait_until_visible,"mobile.driver.back.btn"
+106.Click Back,tap,,"mobile.driver.back.btn"
+107.wait for Wallet,wait_until_visible,"mobile.driver.wallet.btn"
+108.Click Wallet,tap,,"mobile.driver.wallet.btn"
+109.Wait For Topup,wait_until_visible,,"mobile.driver.top_up.btn"
+110.Check Current Balance Displayed,element_present,,"mobile.driver.wallet.current_balance"
+111.Check Transaction History Displaye,element_present,,"mobile.driver.wallet.transaction_history"
+112.Click Topup,tap,,"mobile.driver.top_up.btn"
+113.Wait For Topup Sum,wait_until_visible,,"mobile.driver.top_up.btn"
+114.Click Hundered,tap,,"mobile.driver.top_up_amount.hundred"
+115.Click Proceed,tap,,"mobile.driver.top_up.proceed"
+116.Wait For Contact No,wait_until_visible,,"mobile.driver.top_up.contact_no_box"
+117.Enter Driver Mobile,type,{autoPhone},"mobile.driver.top_up.contact_no_box"
+118.Wait For Payment Options,wait_until_visible,,"mobile.driver.top_up.payment_option"
+119.Wait For Net Banking,wait_until_visible,,"mobile.driver.top_up.net_banking"
+120.Click Net Banking,tap,,"mobile.driver.top_up.net_banking"
+121.Wait For Bob,wait_until_visible,,"mobile.driver.top_up.bob_bank"
+122.Click Bob,tap,,"mobile.driver.top_up.bob_bank"
+123.Wait For Success,wait_until_visible,,"mobile.driver.top_up.succes_popup"
+124.Click Success,tap,,"mobile.driver.top_up.succes_popup"
+125.Wait For Wallet  Back,wait_until_visible,,"mobile.driver.wallet.btn"
+126.Click Back,tap,,"mobile.driver.back.btn"
+127.Drag Page Layout Upward,swipe,up,
+128.Click Back,tap,,"mobile.driver.back.btn"
+129.Reload Driver App Completely,reload_app,driver,
+130.Switch To Web Session,switch_to,web,
+131.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+132.Click Settings Menu,click,,"admin.setting.sidebar.menu"
+133.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+134.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+135.Wait For off,wait,2000,
+136.Select Wallet OFF Option,click,,"admin.setting.site_setting.walletdropdown_option_off"
+137.Click Submit Button,click,,"web.global.action.submit"
+138.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+139.Switch To Driver Session,switch_to,driver,
+140.Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+141.Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+142.Click Agree,tap,,"mobile.driver.agree.btn"
+143.Click Get Started,tap,,"mobile.driver.get_started.btn"
+144.Click Next,tap,,"mobile.driver.next.btn"
+145.Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+146.Click Close,tap,,"mobile.driver.cancel.btn"
+147.Enter Mobile Number,type,{autoPhone} ,"mobile.driver.edit_text.input"
+148.Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+149.Click Continue,tap,,"mobile.driver.continue.btn"
+150.Enter OTP,type,123456,"mobile.driver.edit_text.input"
+151.Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+152.Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+153.Click Hamburger,tap_coordinate,75:209,COORDINATE_MODE
+154.Wait For Account,wait_until_visible,,"mobile.driver.account.heading"
+155.Check Wallet absent,element_absent,,"mobile.driver.wallet.btn"
+156.Load Super Admin,switch_to,web,
+157.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+158.Click Settings Menu,click,,"web.global.menu.settings"
+159.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+160.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+161.Wait For On,wait,2000,
+162.Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
+163.Click Submit Button,click,,"web.global.action.submit"
+164.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+165.Wait For Toast To Hide,wait,3000,</t>
   </si>
   <si>
     <t>1.Load User App,switch_to,user,
@@ -600,71 +784,84 @@
 11. Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
 12. Click Submit Button,click,,"web.global.action.submit"
 13. Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
-14. Load User App,switch_to,user,
-15.Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
-16.Click Get Started,tap,,"mobile.customer.get_started.btn"
-17.Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
-18.Click Next,tap,,"mobile.customer.next.btn"
-19.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
-20.Click Close,tap,,"mobile.customer.cancel.btn"
-21.Enter Mobile Number,type,regression.customer.phone,"mobile.customer.edit_text.input"
-22.Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
-23.Click Continue,tap,,"mobile.customer.continue.btn"
-24.Enter OTP,type,123456,"mobile.customer.otp_input"
-25.Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
-26.Click Finish,tap,,"mobile.customer.finish.btn"
-27.Click Allow Location,tap,,"mobile.customer.location_allow.btn"
-28. Wait For Landing Page,wait_until_visible,,"mobile.customer.home_page.profile_icon"
-29. Click Profile_Menu,tap,,"mobile.customer.home_page.profile_icon"
-30.Wait For Profile,wait_until_visible,,"mobile.customer.account.heading"
-31.wait for Wallet,wait_until_visible,"mobile.customer.wallet.btn"
-32.Check Wallet Present,element_present,,"mobile.customer.wallet.btn"
-33.Click Wallet,tap,,"mobile.customer.wallet.btn"
-34.Wait For Topup,wait_until_visible,,"mobile.customer.top_up.btn"
-35.Reload User App Completely,reload_app,user,
-36. Switch To Web Session,switch_to,web,
-37.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-38.Click Settings Menu,click,,"admin.setting.sidebar.menu"
-39.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
-40.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
-41.Wait For off,wait,2000,
-42. Select Wallet OFF Option,click,,"admin.setting.site_setting.walletdropdown_option_off"
-43.Click Submit Button,click,,"web.global.action.submit"
-44.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
-45.Load User App,switch_to,user,
-46.Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
-47.Click Get Started,tap,,"mobile.customer.get_started.btn"
-48.Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
-49.Click Next,tap,,"mobile.customer.next.btn"
-50.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
-51.Click Close,tap,,"mobile.customer.cancel.btn"
-52.Enter Mobile Number,type,regression.customer.phone,"mobile.customer.edit_text.input"
-53.Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
-54.Click Continue,tap,,"mobile.customer.continue.btn"
-55.Enter OTP,type,123456,"mobile.customer.otp_input"
-56.Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
-57.Click Finish,tap,,"mobile.customer.finish.btn"
-58.Click Allow Location,tap,,"mobile.customer.location_allow.btn"
-59.Wait For Landing Page,wait_until_visible,,"mobile.customer.home_page.profile_icon"
-60.Click Profile_Menu,tap,,"mobile.customer.home_page.profile_icon"
-61.Wait For Profile,wait_until_visible,,"mobile.customer.account.heading"
-62.Check Wallet absent,element_absent,,"mobile.customer.wallet.btn"
-63.Load Super Admin,switch_to,web,
-64.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-65.Click Settings Menu,click,,"web.global.menu.settings"
-66.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
-67.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
-68.Wait For On,wait,2000,
-69.Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
-70.Click Submit Button,click,,"web.global.action.submit"
-71.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
-72.Wait For Toast To Hide,wait,3000,</t>
-  </si>
-  <si>
-    <t>TC_RG_02_Driver_App_Wallet_Verification</t>
-  </si>
-  <si>
-    <t>TC_RG_03_Customer_App_Wallet_Verification</t>
+14. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+15.Click Customer Icon,click,,"admin.menu.customer_icon"
+16.Click Add Customers,click,,"admin.menu.add_customers"
+17.Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
+18.Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+19.Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+20.Enter Contact Number,type,{randomPhone}&gt;&gt;customerPhone,"admin.customer.input_phone"
+21.Enter Emergency Number,type,{randomPhone},"admin.customer.input_Emergency_phone"
+22.Open Gender,click,,"admin.customer.dropdown_gender"
+23.Select Male,click,,"admin.customer.select_gender_male"
+24.Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+25.Click Submit,click,,"web.global.action.submit"
+26.Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+27.Click Dashboard,click,,"web.global.menu.dashboard"
+28.Click Customer Icon,click,,"admin.menu.customer_icon"
+29.Click Verified Customers,click,,"admin.menu.verified_customers"
+30.Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+31.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+32.Wait For Load,wait,2000,
+33. Load User App,switch_to,user,
+34.Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
+35.Click Get Started,tap,,"mobile.customer.get_started.btn"
+36.Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
+37.Click Next,tap,,"mobile.customer.next.btn"
+38.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
+39.Click Close,tap,,"mobile.customer.cancel.btn"
+40.Enter Mobile Number,type,{customerPhone},"mobile.customer.edit_text.input"
+41.Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
+42.Click Continue,tap,,"mobile.customer.continue.btn"
+43.Enter OTP,type,123456,"mobile.customer.otp_input"
+44.Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
+45.Click Finish,tap,,"mobile.customer.finish.btn"
+46.Click Allow Location,tap,,"mobile.customer.location_allow.btn"
+47. Wait For Landing Page,wait_until_visible,,"mobile.customer.home_page.profile_icon"
+48.Click Profile_Menu,tap,,"mobile.customer.home_page.profile_icon"
+49.Wait For Profile,wait_until_visible,,"mobile.customer.account.heading"
+50.wait for Wallet,wait_until_visible,"mobile.customer.wallet.btn"
+51.Check Wallet Present,element_present,,"mobile.customer.wallet.btn"
+52.Click Wallet,tap,,"mobile.customer.wallet.btn"
+53.Wait For Topup,wait_until_visible,,"mobile.customer.top_up.btn"
+54.Reload User App Completely,reload_app,user,
+55.Switch To Web Session,switch_to,web,
+56.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+57.Click Settings Menu,click,,"admin.setting.sidebar.menu"
+58.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+59.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+60.Wait For off,wait,2000,
+61. Select Wallet OFF Option,click,,"admin.setting.site_setting.walletdropdown_option_off"
+62.Click Submit Button,click,,"web.global.action.submit"
+63.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+64.Load User App,switch_to,user,
+65.Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
+66.Click Get Started,tap,,"mobile.customer.get_started.btn"
+67.Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
+68.Click Next,tap,,"mobile.customer.next.btn"
+69.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
+70.Click Close,tap,,"mobile.customer.cancel.btn"
+71.Enter Mobile Number,type,{customerPhone},"mobile.customer.edit_text.input"
+72.Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
+73.Click Continue,tap,,"mobile.customer.continue.btn"
+74.Enter OTP,type,123456,"mobile.customer.otp_input"
+75.Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
+76.Click Finish,tap,,"mobile.customer.finish.btn"
+77.Click Allow Location,tap,,"mobile.customer.location_allow.btn"
+78.Wait For Landing Page,wait_until_visible,,"mobile.customer.home_page.profile_icon"
+79.Click Profile_Menu,tap,,"mobile.customer.home_page.profile_icon"
+80.Wait For Profile,wait_until_visible,,"mobile.customer.account.heading"
+81.Check Wallet absent,element_absent,,"mobile.customer.wallet.btn"
+82.Load Super Admin,switch_to,web,
+83.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+84.Click Settings Menu,click,,"web.global.menu.settings"
+85.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+86.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+87.Wait For On,wait,2000,
+88.Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
+89.Click Submit Button,click,,"web.global.action.submit"
+90.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+91.Wait For Toast To Hide,wait,3000,</t>
   </si>
 </sst>
 </file>
@@ -1119,8 +1316,8 @@
     <col min="6" max="6" width="45.77734375" customWidth="1"/>
     <col min="7" max="7" width="71.44140625" customWidth="1"/>
     <col min="8" max="8" width="40.44140625" customWidth="1"/>
-    <col min="9" max="9" width="61.88671875" customWidth="1"/>
-    <col min="10" max="10" width="32.88671875" customWidth="1"/>
+    <col min="9" max="9" width="25.88671875" customWidth="1"/>
+    <col min="10" max="10" width="66.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1166,7 +1363,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>25</v>
@@ -1175,7 +1372,7 @@
         <v>26</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -1183,7 +1380,9 @@
       <c r="I2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -1264,7 +1463,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>29</v>
@@ -1273,7 +1472,7 @@
         <v>31</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -1282,7 +1481,7 @@
         <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
